--- a/teaching/advanced-econometrics/labs/20-specification-report/specification_report.xlsx
+++ b/teaching/advanced-econometrics/labs/20-specification-report/specification_report.xlsx
@@ -6444,10 +6444,10 @@
         <x:v>interaction</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>Treatment times centered baseline</x:v>
+        <x:v>Treatment times the raw baseline covariate x</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>treat × baseline</x:v>
+        <x:v>treat × x</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>No missing values.</x:v>
